--- a/pose的舊資料/B3_配對診斷_重新標註-2.xlsx
+++ b/pose的舊資料/B3_配對診斷_重新標註-2.xlsx
@@ -453,13 +453,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>19.029</v>
+        <v>19.256</v>
       </c>
       <c r="C2" t="n">
-        <v>0.0883</v>
+        <v>0.0926</v>
       </c>
       <c r="D2" t="n">
-        <v>0.6879999999999999</v>
+        <v>0.669</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
@@ -474,13 +474,13 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>19.537</v>
+        <v>19.15</v>
       </c>
       <c r="C3" t="n">
-        <v>0.1122</v>
+        <v>0.1132</v>
       </c>
       <c r="D3" t="n">
-        <v>0.631</v>
+        <v>0.583</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
@@ -495,10 +495,10 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>11.167</v>
+        <v>-2.34</v>
       </c>
       <c r="C4" t="n">
-        <v>23.148</v>
+        <v>18.882</v>
       </c>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr">
@@ -536,7 +536,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>025_jpg.rf.f06a8c53e7f4b681c9427183b37f5bc2.jpg</t>
+          <t>025_jpg.rf.bd162846056d96289581b8b68a4cd15e.jpg</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -548,7 +548,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>033_jpg.rf.f069be44f0966621607332c12f0c9ee6.jpg</t>
+          <t>033_jpg.rf.d3280fd4c1a5d0ad4febcd03cbb7b159.jpg</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -1202,7 +1202,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>yolo像素預測_11_batch4_重新標註-2.xlsx</t>
+          <t>yolo像素預測_26_batch4.xlsx</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
